--- a/StructureDefinition-PSSCodedRating.xlsx
+++ b/StructureDefinition-PSSCodedRating.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-27T22:55:39+00:00</t>
+    <t>2025-03-02T19:26:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PSSCodedRating.xlsx
+++ b/StructureDefinition-PSSCodedRating.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-02T19:26:20+00:00</t>
+    <t>2025-03-02T19:33:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PSSCodedRating.xlsx
+++ b/StructureDefinition-PSSCodedRating.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-02T19:33:38+00:00</t>
+    <t>2025-03-03T11:01:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PSSCodedRating.xlsx
+++ b/StructureDefinition-PSSCodedRating.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-03T11:01:42+00:00</t>
+    <t>2025-03-06T11:29:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PSSCodedRating.xlsx
+++ b/StructureDefinition-PSSCodedRating.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-06T11:29:33+00:00</t>
+    <t>2025-03-06T11:49:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PSSCodedRating.xlsx
+++ b/StructureDefinition-PSSCodedRating.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-06T11:49:07+00:00</t>
+    <t>2025-03-06T20:18:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PSSCodedRating.xlsx
+++ b/StructureDefinition-PSSCodedRating.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://www.ehealth.fgov.be/standards/fhir/medication/StructureDefinition/PSSCodedRating</t>
+    <t>https://www.ehealth.fgov.be/standards/fhir/pss/StructureDefinition/PSSCodedRating</t>
   </si>
   <si>
     <t>Version</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-06T20:18:44+00:00</t>
+    <t>2025-03-06T20:59:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
